--- a/doc/引脚分配.xlsx
+++ b/doc/引脚分配.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="66">
   <si>
     <r>
       <rPr>
@@ -223,6 +223,9 @@
     </r>
   </si>
   <si>
+    <t>D0-D7 3-10  A0-A7 13-20  wr-23 rd-25 编码器A 24 B 26 进料信号27 相机28 吹料 29（良）30（劣）</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -603,153 +606,6 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>控制线</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>WR (写)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第 12 脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>L9</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EXT1_10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>RD (读)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第 14 脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>P9</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EXT1_12</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>CS (片选)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第 16 脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>M10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EXT1_14</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
       <t>地址线</t>
     </r>
   </si>
@@ -932,15 +788,6 @@
       </rPr>
       <t>EXT1_15</t>
     </r>
-  </si>
-  <si>
-    <t>T9</t>
-  </si>
-  <si>
-    <t>T10</t>
-  </si>
-  <si>
-    <t>T11</t>
   </si>
 </sst>
 </file>
@@ -953,7 +800,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -979,13 +826,6 @@
       <color rgb="FF444746"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1482,133 +1322,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1625,7 +1465,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1939,8 +1779,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" ht="58.35" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -1993,7 +1833,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="43.95" spans="1:5">
+    <row r="4" ht="43.95" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -2008,286 +1848,244 @@
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" ht="15.15" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" ht="15.15" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="15.15" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" ht="15.15" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" ht="15.15" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" ht="15.15" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" ht="15.15" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="15.15" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="13" ht="28.35" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>52</v>
-      </c>
+    <row r="13" ht="14.55" spans="1:5">
+      <c r="A13" s="1"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="2"/>
     </row>
-    <row r="14" ht="28.35" spans="1:5">
-      <c r="A14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>56</v>
-      </c>
+    <row r="14" ht="14.55" spans="1:5">
+      <c r="A14" s="1"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="2"/>
     </row>
-    <row r="15" ht="29.55" spans="1:5">
-      <c r="A15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>60</v>
-      </c>
+    <row r="15" ht="14.55" spans="1:5">
+      <c r="A15" s="1"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="2"/>
     </row>
     <row r="16" ht="15.15" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" ht="28.35" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" ht="28.35" spans="1:5">
       <c r="A18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="19" ht="28.35" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="21" spans="3:4">
-      <c r="C21">
-        <v>21</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>78</v>
-      </c>
+    <row r="21" spans="4:4">
+      <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="3:4">
-      <c r="C22">
-        <v>23</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>79</v>
-      </c>
+    <row r="22" spans="4:4">
+      <c r="D22" s="4"/>
     </row>
-    <row r="23" spans="3:4">
-      <c r="C23">
-        <v>25</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>80</v>
-      </c>
+    <row r="23" spans="4:4">
+      <c r="D23" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/引脚分配.xlsx
+++ b/doc/引脚分配.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9324"/>
+    <workbookView windowWidth="27948" windowHeight="12575" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="地址分配" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -29,765 +29,1148 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="66">
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>信号类型</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>CH368 端引脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>FPGA P2 排针脚位</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>FPGA 物理引脚 (Quartus用)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对应说明 (结合你发的引脚图)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>系统</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(板载)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>M16</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="108">
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顶层代码信号名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>物理意义</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你的 P2 排针要求</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Quartus 物理引脚号 (Location)</t>
+    </r>
+  </si>
+  <si>
+    <t>D0-D7 3-10  A0-A7 13-20  wr-23 rd-25 编码器A 24 B 26 进料信号27 相机28 吹料 29（良）30（劣）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color rgb="FF444746"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>clk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> (24MHz 系统时钟)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>M12</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>ch368_data[0]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 3 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_M8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color rgb="FF444746"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>rst_n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> (复位信号，低有效)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>电源</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>GND</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>必须与 FPGA 共地！</t>
-    </r>
-  </si>
-  <si>
-    <t>D0-D7 3-10  A0-A7 13-20  wr-23 rd-25 编码器A 24 B 26 进料信号27 相机28 吹料 29（良）30（劣）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>数据线</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>D0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第 3 脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>M8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EXT1_1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>D1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第 4 脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>L8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EXT1_2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>D2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第 5 脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>L7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EXT1_3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>D3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第 6 脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>T6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EXT1_4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>D4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第 7 脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>R6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EXT1_5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>D5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第 8 脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>N8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EXT1_6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>D6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第 9 脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>P8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EXT1_7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>D7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第 10 脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>K9</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EXT1_8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>地址线</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>A0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第 11 脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>K10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EXT1_9</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>A1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第 13 脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>M9</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EXT1_11</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>A2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第 15 脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>N9</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EXT1_13</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>A3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第 17 脚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>P11</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EXT1_15</t>
-    </r>
+      <t>ch368_data[1]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 4 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_L8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_data[2]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 5 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_L7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_data[3]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 6 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_T6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_data[4]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 7 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_R6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_data[5]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 8 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_N8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_data[6]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 9 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_P8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_data[7]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 10 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_K9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[0]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 13 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_M9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[1]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 14 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_P9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[2]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 15 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_N9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[3]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 16 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_M10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[4]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 17 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_P11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[5]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 18 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_N11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[6]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 19 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_R7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[7]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 20 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_L10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_wr_n</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>写使能 (WR)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 23 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_T9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_rd_n</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>读使能 (RD)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 25 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_T10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>enc_a</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>编码器 A 相</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 24 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_T8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>enc_b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>编码器 B 相</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 26 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_R9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sensor_in</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>进料光电传感器</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 27 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_T11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>camera_out</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>相机触发输出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 28 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_R10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>reject_out</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>剔除气缸输出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 29 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_R14</t>
+    </r>
+  </si>
+  <si>
+    <t>地址按字节（16位）</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>数据</t>
+  </si>
+  <si>
+    <t>读写</t>
+  </si>
+  <si>
+    <t>固定0x5A</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>工件是否进入</t>
+  </si>
+  <si>
+    <t>位置低字节</t>
+  </si>
+  <si>
+    <t>位置高字节</t>
+  </si>
+  <si>
+    <t>工件状态</t>
+  </si>
+  <si>
+    <t>w</t>
   </si>
 </sst>
 </file>
@@ -816,14 +1199,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
+      <color rgb="FF444746"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF444746"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -1166,7 +1550,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1186,21 +1570,6 @@
       </top>
       <bottom style="medium">
         <color rgb="FF1F1F1F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1328,7 +1697,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1340,34 +1709,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1452,7 +1821,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1464,9 +1833,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1779,10 +2145,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" ht="58.35" spans="1:5">
+    <row r="1" ht="70.95" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1795,297 +2161,355 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="57.15" spans="1:5">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="29.55" spans="1:4">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="43.95" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>6</v>
+    <row r="3" ht="29.55" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" ht="43.95" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
+    </row>
+    <row r="4" ht="29.55" spans="1:4">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H4" t="s">
+      <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" ht="15.15" spans="1:5">
-      <c r="A5" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="5" ht="29.55" spans="1:4">
+      <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="C5" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="6" ht="29.55" spans="1:4">
+      <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="C6" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="D6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    <row r="7" ht="29.55" spans="1:4">
+      <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" ht="15.15" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="8" ht="29.55" spans="1:4">
+      <c r="A8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="C8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="D8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" ht="15.15" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2" t="s">
+    <row r="9" ht="29.55" spans="1:4">
+      <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="C9" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="10" ht="15.15" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="10" ht="15.15" spans="1:4">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" ht="29.55" spans="1:4">
+      <c r="A11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" ht="15.15" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="2" t="s">
+    <row r="12" ht="29.55" spans="1:4">
+      <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="12" ht="15.15" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="2" t="s">
+    <row r="13" ht="29.55" spans="1:4">
+      <c r="A13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" ht="14.55" spans="1:5">
-      <c r="A13" s="1"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" ht="14.55" spans="1:5">
-      <c r="A14" s="1"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" ht="14.55" spans="1:5">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" ht="15.15" spans="1:5">
-      <c r="A16" s="1" t="s">
+    <row r="14" ht="29.55" spans="1:4">
+      <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" ht="29.55" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" ht="29.55" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="D16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" ht="28.35" spans="1:5">
-      <c r="A17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" ht="29.55" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" ht="28.35" spans="1:5">
-      <c r="A18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" ht="29.55" spans="1:4">
+      <c r="A18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" ht="28.35" spans="1:5">
-      <c r="A19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="4:4">
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" spans="4:4">
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="4:4">
-      <c r="D23" s="4"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" ht="15.15" spans="1:4">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" ht="29.55" spans="1:4">
+      <c r="A20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" ht="29.55" spans="1:4">
+      <c r="A21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" ht="15.15" spans="1:4">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" ht="29.55" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" ht="29.55" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" ht="15.15" spans="1:4">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" ht="29.55" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" ht="29.55" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" ht="29.55" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>96</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2097,9 +2521,86 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="4" max="4" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/doc/引脚分配.xlsx
+++ b/doc/引脚分配.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="地址分配" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="436">
   <si>
     <r>
       <rPr>
@@ -1140,37 +1141,5466 @@
     </r>
   </si>
   <si>
-    <t>地址按字节（16位）</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>数据</t>
-  </si>
-  <si>
-    <t>读写</t>
-  </si>
-  <si>
-    <t>固定0x5A</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>工件是否进入</t>
-  </si>
-  <si>
-    <t>位置低字节</t>
-  </si>
-  <si>
-    <t>位置高字节</t>
-  </si>
-  <si>
-    <t>工件状态</t>
-  </si>
-  <si>
-    <t>w</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>十六进制地址 (HEX)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>十进制地址 (DEC)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>读/写 (R/W)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>变量名称 / 用途说明</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位宽及格式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x00</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>R</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>底层通信测试</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>读出固定值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x5A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，用于验证总线是否通畅。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x02</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>R/W</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>电机状态控制</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Bit 0: 电机使能 (1=启动, 0=停止)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Bit 1: 电机方向</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x03</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>电机速度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0~255</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，直接输出给 PWM 模块。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x08</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吹料位置 (最低位 LSB)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>结合 0x09, 0x0A, 0x0B 拼接为完整的 32 位吹气位置。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(例如 0x08 写最低位，0x0B 写最高位)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x09</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吹料位置 (次低位)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>同上</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x0A</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吹料位置 (次高位)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x0B</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吹料位置 (最高位 MSB)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x0E</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>光源提前延时</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>light_delay_ms</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：单位为毫秒 (默认</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>即 2ms)。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x0F</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>气阀吹气时长</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>blow_time_ms</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：单位为毫秒 (默认</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>即 50ms)。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>物理相机编号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>基地址 (HEX)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址范围 (占用 4 字节)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>读/写</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>详细说明</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1# 相机</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x23</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1号相机的 32位 触发位置 (0x20为最低位，0x23为最高位)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2# 相机</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x24</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x27</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2号相机的 32位 触发位置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3# 相机</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x28</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x2A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x2B</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3号相机的 32位 触发位置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4# 相机</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x2C</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x2C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x2D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x2E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x2F</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4号相机的 32位 触发位置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5# 相机</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x33</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5号相机的 32位 触发位置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6# 相机</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x34</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x34</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x36</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x37</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6号相机的 32位 触发位置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7# 相机</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x38</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x39</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x3A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x3B</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7号相机的 32位 触发位置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8# 相机</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x3C</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x3C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x3D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x3E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x3F</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8号相机的 32位 触发位置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>逻辑工件 ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>状态地址 (HEX)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>位置地址 (占用 4 字节)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>状态代码对照表</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>工件 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x81</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x82</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x83</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x84</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>状态读写定义：</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>•</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：无料 (槽位未激活)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>•</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：空闲滑行 (槽位已分配)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>•</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xAA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：已鉴定为良品</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>•</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xEE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：已鉴定为次品</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(写入</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xAA</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xEE</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>即可改变工件命运)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>工件 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x88</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x89</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x8A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x8B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x8C</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(同上)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>工件 2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x90</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x91</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x92</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x93</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x94</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>工件 3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x98</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x99</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x9A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x9B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x9C</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>工件 4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xA0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xA1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xA2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xA3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xA4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>工件 5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xA8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xA9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xAA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xAB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xAC</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>工件 6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xB0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xB1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xB2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xB3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xB4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>工件 7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xB8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xB9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xBA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xBB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0xBC</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你的 P2/P3 排针要求</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_M8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_L8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_L7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_T6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_R6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_N8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_P8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_K9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_M9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_P9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_N9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_M10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_P11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_N11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_R7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_L10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_T9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_T10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_T8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_R9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_T11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_R10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_R14</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1#光源</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 3 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_A15</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1#相机</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 5 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_A14</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2#光源</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 7 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_F11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2#相机</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 9 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_A13</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3#光源</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 11 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_A12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3#相机</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 13 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_A11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4#光源</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 15 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_A10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4#相机</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 17 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_A9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5#光源</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 19 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_D8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5#相机</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 21 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_B7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6#光源</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 23 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_B6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6#相机</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 25 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_D11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(见上方冲突提醒)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1#电磁阀吹气</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 27 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_E10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2#电磁阀吹气</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 29 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_D9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3#电磁阀吹气</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 31 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_F9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4#电磁阀吹气</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 33 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_E8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>[未定义/留空]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 35 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_E7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 37 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_B5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>电机脉冲输出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 36 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_C6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>NC (空置)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>编码器A相差分输入</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 38 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_E11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>编码器B相差分输入</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 40 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_F6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>下料控制</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 4 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_B14</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>震动盘控制</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 6 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_B13</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>电机使能</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 8 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 10 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_B12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三色灯</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 12 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_B11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 14 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_B10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 16 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_B9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 18 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_C9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>光纤输入</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 20 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_A7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>急停</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 22 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_A6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 24 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_A5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 26 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_C11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 28 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_F10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 30 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_E9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 32 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_F8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顶层代码信号名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>物理意义</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你的 P2/P3 排针要求</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Quartus 物理引脚号 (Location)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_data[0]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 3 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_M8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_data[1]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 4 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_L8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_data[2]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 5 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_L7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_data[3]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 6 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_T6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_data[4]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 7 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_R6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_data[5]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 8 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_N8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_data[6]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 9 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_P8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_data[7]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据位 D7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 10 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_K9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[0]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 13 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_M9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[1]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 14 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_P9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[2]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 15 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_N9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[3]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 16 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_M10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[4]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 17 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_P11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[5]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 18 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_N11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[6]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 19 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_R7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_addr[7]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地址位 A7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 20 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_L10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_wr_n</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>写使能 (WR)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 23 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_T9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch368_rd_n</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>读使能 (RD)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P2 - 第 25 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_T10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>light_out</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1#光源</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 3 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_A15</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>camera_out</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1#相机</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 5 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_A14</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>reject_out</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2#电磁阀吹气</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 29 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_D9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>motor_pwm_out</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>电机脉冲输出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 36 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_C6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>NC (空置)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>enc_a</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>编码器A相差分输入</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 38 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_E11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>enc_b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>编码器B相差分输入</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 40 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_F6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>motor_en_out</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>电机使能</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 8 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_D12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sensor_in</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>光纤输入</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>P3 - 第 20 脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PIN_A7</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1183,13 +6613,39 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF444746"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF444746"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1209,6 +6665,25 @@
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF444746"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1354,6 +6829,20 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF444746"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1550,7 +7039,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1568,6 +7057,43 @@
       <top style="medium">
         <color rgb="FF1F1F1F"/>
       </top>
+      <bottom style="medium">
+        <color rgb="FF1F1F1F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F1F1F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F1F1F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F1F1F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F1F1F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F1F1F"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F1F1F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F1F1F"/>
+      </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FF1F1F1F"/>
       </bottom>
@@ -1691,148 +7217,199 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2149,16 +7726,16 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" ht="70.95" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
@@ -2166,348 +7743,348 @@
       </c>
     </row>
     <row r="2" ht="29.55" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" ht="29.55" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" ht="29.55" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" ht="29.55" spans="1:4">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" ht="29.55" spans="1:4">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" ht="29.55" spans="1:4">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="5" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" ht="29.55" spans="1:4">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" ht="29.55" spans="1:4">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" ht="15.15" spans="1:4">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" ht="29.55" spans="1:4">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="5" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="12" ht="29.55" spans="1:4">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" ht="29.55" spans="1:4">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="5" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="14" ht="29.55" spans="1:4">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="5" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="15" ht="29.55" spans="1:4">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="5" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="16" ht="29.55" spans="1:4">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="5" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="17" ht="29.55" spans="1:4">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="5" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="18" ht="29.55" spans="1:4">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="19" ht="15.15" spans="1:4">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" ht="29.55" spans="1:4">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="5" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="21" ht="29.55" spans="1:4">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="5" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="22" ht="15.15" spans="1:4">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
     </row>
     <row r="23" ht="29.55" spans="1:4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="24" ht="29.55" spans="1:4">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="25" ht="15.15" spans="1:4">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
     </row>
     <row r="26" ht="29.55" spans="1:4">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="27" ht="29.55" spans="1:4">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="5" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="28" ht="29.55" spans="1:4">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="5" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2521,86 +8098,610 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
+    <row r="1" ht="43.95" spans="1:5">
+      <c r="A1" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C1" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" s="9" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
+      <c r="E1" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" ht="43.95" spans="1:5">
+      <c r="A2" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="11">
         <v>0</v>
       </c>
-      <c r="D2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
+      <c r="C2" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" ht="30.3" customHeight="1" spans="1:5">
+      <c r="A3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="11">
+        <v>2</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" ht="15.15" spans="1:5">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="14"/>
+    </row>
+    <row r="5" ht="15.15" spans="1:5">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" ht="29.55" spans="1:5">
+      <c r="A6" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="11">
+        <v>3</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" ht="44.7" customHeight="1" spans="1:5">
+      <c r="A7" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="11">
+        <v>8</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" ht="15.15" spans="1:5">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="14"/>
+    </row>
+    <row r="9" ht="43.95" spans="1:5">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" ht="43.95" spans="1:5">
+      <c r="A10" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="11">
+        <v>9</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" ht="43.95" spans="1:5">
+      <c r="A11" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="11">
         <v>10</v>
       </c>
-      <c r="D9" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
+      <c r="C11" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" ht="58.35" spans="1:5">
+      <c r="A12" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="11">
         <v>11</v>
       </c>
-      <c r="D10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>13</v>
-      </c>
-      <c r="D12" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="C12" s="12" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16">
-        <v>30</v>
-      </c>
+      <c r="D12" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" ht="43.95" spans="1:5">
+      <c r="A13" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" s="11">
+        <v>14</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" ht="43.95" spans="1:5">
+      <c r="A14" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" s="11">
+        <v>15</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" ht="15.15" spans="1:5">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" ht="58.35" spans="1:5">
+      <c r="A16" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" ht="58.35" spans="1:5">
+      <c r="A17" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" ht="58.35" spans="1:5">
+      <c r="A18" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" ht="58.35" spans="1:5">
+      <c r="A19" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" ht="58.35" spans="1:5">
+      <c r="A20" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" ht="58.35" spans="1:5">
+      <c r="A21" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" ht="58.35" spans="1:5">
+      <c r="A22" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" ht="58.35" spans="1:5">
+      <c r="A23" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" ht="58.35" spans="1:5">
+      <c r="A24" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" ht="15.15" spans="1:5">
+      <c r="A25" s="9"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="17"/>
+    </row>
+    <row r="26" ht="58.35" spans="1:5">
+      <c r="A26" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" s="18"/>
+    </row>
+    <row r="27" ht="44.7" customHeight="1" spans="1:5">
+      <c r="A27" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27" s="18"/>
+    </row>
+    <row r="28" ht="15.15" spans="1:5">
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="18"/>
+    </row>
+    <row r="29" ht="58.35" spans="1:5">
+      <c r="A29" s="9"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="E29" s="18"/>
+    </row>
+    <row r="30" ht="15.15" spans="1:5">
+      <c r="A30" s="9"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="18"/>
+    </row>
+    <row r="31" ht="58.35" spans="1:5">
+      <c r="A31" s="9"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="E31" s="18"/>
+    </row>
+    <row r="32" ht="15.15" spans="1:5">
+      <c r="A32" s="9"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="18"/>
+    </row>
+    <row r="33" ht="43.95" spans="1:5">
+      <c r="A33" s="9"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="E33" s="18"/>
+    </row>
+    <row r="34" ht="15.15" spans="1:5">
+      <c r="A34" s="9"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="18"/>
+    </row>
+    <row r="35" ht="43.95" spans="1:5">
+      <c r="A35" s="9"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="E35" s="18"/>
+    </row>
+    <row r="36" ht="15.15" spans="1:5">
+      <c r="A36" s="9"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="18"/>
+    </row>
+    <row r="37" ht="72.75" spans="1:5">
+      <c r="A37" s="9"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="E37" s="18"/>
+    </row>
+    <row r="38" ht="58.35" spans="1:5">
+      <c r="A38" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E38" s="18"/>
+    </row>
+    <row r="39" ht="58.35" spans="1:5">
+      <c r="A39" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E39" s="18"/>
+    </row>
+    <row r="40" ht="58.35" spans="1:5">
+      <c r="A40" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E40" s="18"/>
+    </row>
+    <row r="41" ht="58.35" spans="1:5">
+      <c r="A41" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E41" s="18"/>
+    </row>
+    <row r="42" ht="58.35" spans="1:5">
+      <c r="A42" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E42" s="18"/>
+    </row>
+    <row r="43" ht="58.35" spans="1:5">
+      <c r="A43" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E43" s="18"/>
+    </row>
+    <row r="44" ht="58.35" spans="1:5">
+      <c r="A44" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E44" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A27:A37"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B27:B37"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C27:C37"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="D7:D9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -2610,11 +8711,1270 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:D61"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" ht="70.95" spans="1:4">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="29.55" spans="1:4">
+      <c r="A2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" ht="29.55" spans="1:4">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" ht="29.55" spans="1:4">
+      <c r="A4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" ht="29.55" spans="1:4">
+      <c r="A5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6" ht="29.55" spans="1:4">
+      <c r="A6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" ht="29.55" spans="1:4">
+      <c r="A7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" ht="29.55" spans="1:4">
+      <c r="A8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9" ht="29.55" spans="1:4">
+      <c r="A9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" ht="29.55" spans="1:4">
+      <c r="A10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="11" ht="29.55" spans="1:4">
+      <c r="A11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="12" ht="29.55" spans="1:4">
+      <c r="A12" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13" ht="29.55" spans="1:4">
+      <c r="A13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" ht="29.55" spans="1:4">
+      <c r="A14" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="15" ht="29.55" spans="1:4">
+      <c r="A15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" ht="29.55" spans="1:4">
+      <c r="A16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" ht="29.55" spans="1:4">
+      <c r="A17" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" ht="29.55" spans="1:4">
+      <c r="A18" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" ht="29.55" spans="1:4">
+      <c r="A19" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" ht="29.55" spans="1:4">
+      <c r="A20" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" ht="29.55" spans="1:4">
+      <c r="A21" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="22" ht="29.55" spans="1:4">
+      <c r="A22" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="23" ht="29.55" spans="1:4">
+      <c r="A23" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="24" ht="29.55" spans="1:4">
+      <c r="A24" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="25" ht="29.55" spans="1:4">
+      <c r="A25" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="26" ht="29.55" spans="1:4">
+      <c r="A26" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="27" ht="29.55" spans="1:4">
+      <c r="A27" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28" ht="29.55" spans="1:4">
+      <c r="A28" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="29" ht="29.55" spans="1:4">
+      <c r="A29" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="30" ht="29.55" spans="1:4">
+      <c r="A30" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="31" ht="29.55" spans="1:4">
+      <c r="A31" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="32" ht="29.55" spans="1:4">
+      <c r="A32" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="33" ht="29.55" spans="1:4">
+      <c r="A33" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" ht="29.55" spans="1:4">
+      <c r="A34" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="35" ht="29.55" spans="1:4">
+      <c r="A35" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="36" ht="57.75" spans="1:4">
+      <c r="A36" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="37" ht="29.55" spans="1:4">
+      <c r="A37" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="38" ht="29.55" spans="1:4">
+      <c r="A38" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="39" ht="29.55" spans="1:4">
+      <c r="A39" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="40" ht="29.55" spans="1:4">
+      <c r="A40" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="41" ht="29.55" spans="1:4">
+      <c r="A41" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="42" ht="29.55" spans="1:4">
+      <c r="A42" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="43" ht="29.55" spans="1:4">
+      <c r="A43" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="44" ht="29.55" spans="1:4">
+      <c r="A44" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="45" ht="43.95" spans="1:4">
+      <c r="A45" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="46" ht="43.95" spans="1:4">
+      <c r="A46" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="47" ht="29.55" spans="1:4">
+      <c r="A47" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="48" ht="29.55" spans="1:4">
+      <c r="A48" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="49" ht="57.75" spans="1:4">
+      <c r="A49" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="50" ht="29.55" spans="1:4">
+      <c r="A50" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="51" ht="29.55" spans="1:4">
+      <c r="A51" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="52" ht="29.55" spans="1:4">
+      <c r="A52" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="53" ht="29.55" spans="1:4">
+      <c r="A53" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="54" ht="29.55" spans="1:4">
+      <c r="A54" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="55" ht="29.55" spans="1:4">
+      <c r="A55" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="56" ht="29.55" spans="1:4">
+      <c r="A56" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="57" ht="29.55" spans="1:4">
+      <c r="A57" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="58" ht="29.55" spans="1:4">
+      <c r="A58" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="59" ht="29.55" spans="1:4">
+      <c r="A59" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="60" ht="29.55" spans="1:4">
+      <c r="A60" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="61" ht="29.55" spans="1:4">
+      <c r="A61" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>325</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" ht="72.75" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" ht="29.55" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="3" ht="29.55" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="4" ht="29.55" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="5" ht="29.55" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="6" ht="29.55" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="7" ht="29.55" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" ht="29.55" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="9" ht="29.55" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="10" ht="29.55" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="11" ht="29.55" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="12" ht="29.55" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="13" ht="29.55" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="14" ht="29.55" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="15" ht="29.55" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="16" ht="29.55" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="17" ht="29.55" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="18" ht="29.55" spans="1:4">
+      <c r="A18" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="19" ht="29.55" spans="1:4">
+      <c r="A19" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="20" ht="29.55" spans="1:4">
+      <c r="A20" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="21" ht="29.55" spans="1:4">
+      <c r="A21" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="22" ht="29.55" spans="1:4">
+      <c r="A22" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="23" ht="29.55" spans="1:4">
+      <c r="A23" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="24" ht="29.55" spans="1:4">
+      <c r="A24" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="25" ht="43.95" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="26" ht="43.95" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="27" ht="29.55" spans="1:4">
+      <c r="A27" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="28" ht="29.55" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>435</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/doc/引脚分配.xlsx
+++ b/doc/引脚分配.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12575"/>
+    <workbookView windowWidth="22188" windowHeight="9324"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="532">
   <si>
     <r>
       <rPr>
@@ -88,21 +88,6 @@
       </rPr>
       <t>Quartus 物理引脚号 (Location)</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>PCB接口丝印</t>
-    </r>
-  </si>
-  <si>
-    <t>D0-D7 3-10  A0-A7 13-20  wr-23 rd-25 编码器A 24 B 26 进料信号27 相机28 吹料 29（良）30（劣）</t>
   </si>
   <si>
     <r>
@@ -8868,14 +8853,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F66"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="13.6666666666667" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="72.75" spans="1:6">
+    <row r="1" ht="72.75" spans="1:5">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -8888,934 +8873,929 @@
       <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
+      <c r="E1" s="18"/>
     </row>
     <row r="2" ht="29.55" spans="1:5">
       <c r="A2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>9</v>
       </c>
       <c r="E2" s="22"/>
     </row>
     <row r="3" ht="29.55" spans="1:5">
       <c r="A3" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>11</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>13</v>
       </c>
       <c r="E3" s="22"/>
     </row>
     <row r="4" ht="29.55" spans="1:5">
       <c r="A4" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="D4" s="21" t="s">
         <v>15</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>17</v>
       </c>
       <c r="E4" s="22"/>
     </row>
     <row r="5" ht="29.55" spans="1:5">
       <c r="A5" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>19</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>21</v>
       </c>
       <c r="E5" s="22"/>
     </row>
     <row r="6" ht="29.55" spans="1:5">
       <c r="A6" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="D6" s="21" t="s">
         <v>23</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>25</v>
       </c>
       <c r="E6" s="22"/>
     </row>
     <row r="7" ht="29.55" spans="1:5">
       <c r="A7" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="D7" s="21" t="s">
         <v>27</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>29</v>
       </c>
       <c r="E7" s="22"/>
     </row>
     <row r="8" ht="29.55" spans="1:5">
       <c r="A8" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="D8" s="21" t="s">
         <v>31</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>33</v>
       </c>
       <c r="E8" s="22"/>
     </row>
     <row r="9" ht="29.55" spans="1:5">
       <c r="A9" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="D9" s="21" t="s">
         <v>35</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>37</v>
       </c>
       <c r="E9" s="22"/>
     </row>
     <row r="10" ht="29.55" spans="1:5">
       <c r="A10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="D10" s="21" t="s">
         <v>39</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>41</v>
       </c>
       <c r="E10" s="22"/>
     </row>
     <row r="11" ht="29.55" spans="1:5">
       <c r="A11" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="D11" s="21" t="s">
         <v>43</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>45</v>
       </c>
       <c r="E11" s="22"/>
     </row>
     <row r="12" ht="29.55" spans="1:5">
       <c r="A12" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="D12" s="21" t="s">
         <v>47</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>49</v>
       </c>
       <c r="E12" s="22"/>
     </row>
     <row r="13" ht="29.55" spans="1:5">
       <c r="A13" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="D13" s="21" t="s">
         <v>51</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>53</v>
       </c>
       <c r="E13" s="22"/>
     </row>
     <row r="14" ht="29.55" spans="1:5">
       <c r="A14" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="D14" s="21" t="s">
         <v>55</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>57</v>
       </c>
       <c r="E14" s="22"/>
     </row>
     <row r="15" ht="29.55" spans="1:5">
       <c r="A15" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="D15" s="21" t="s">
         <v>59</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>61</v>
       </c>
       <c r="E15" s="22"/>
     </row>
     <row r="16" ht="29.55" spans="1:5">
       <c r="A16" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="D16" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>65</v>
       </c>
       <c r="E16" s="22"/>
     </row>
     <row r="17" ht="29.55" spans="1:5">
       <c r="A17" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="D17" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>69</v>
       </c>
       <c r="E17" s="22"/>
     </row>
     <row r="18" ht="29.55" spans="1:5">
       <c r="A18" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="D18" s="21" t="s">
         <v>71</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>73</v>
       </c>
       <c r="E18" s="22"/>
     </row>
     <row r="19" ht="29.55" spans="1:5">
       <c r="A19" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="D19" s="21" t="s">
         <v>75</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>77</v>
       </c>
       <c r="E19" s="22"/>
     </row>
     <row r="20" ht="29.55" spans="1:5">
       <c r="A20" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="D20" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="E20" s="23" t="s">
         <v>80</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="21" ht="29.55" spans="1:5">
       <c r="A21" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="D21" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="E21" s="23" t="s">
         <v>85</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="22" ht="29.55" spans="1:5">
       <c r="A22" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="D22" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="E22" s="23" t="s">
         <v>90</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="23" ht="29.55" spans="1:5">
       <c r="A23" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B23" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="E23" s="23" t="s">
         <v>94</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="24" ht="29.55" spans="1:5">
       <c r="A24" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B24" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="E24" s="23" t="s">
         <v>98</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="25" ht="29.55" spans="1:5">
       <c r="A25" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B25" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="E25" s="23" t="s">
         <v>102</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="26" ht="29.55" spans="1:5">
       <c r="A26" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B26" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="E26" s="23" t="s">
         <v>106</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="27" ht="29.55" spans="1:5">
       <c r="A27" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B27" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="E27" s="23" t="s">
         <v>110</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="28" ht="29.55" spans="1:5">
       <c r="A28" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B28" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="E28" s="23" t="s">
         <v>114</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="29" ht="29.55" spans="1:5">
       <c r="A29" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B29" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="E29" s="23" t="s">
         <v>118</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="30" ht="29.55" spans="1:5">
       <c r="A30" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B30" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="E30" s="23" t="s">
         <v>122</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="31" ht="29.55" spans="1:5">
       <c r="A31" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B31" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="E31" s="23" t="s">
         <v>126</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="32" ht="29.55" spans="1:5">
       <c r="A32" s="20"/>
       <c r="B32" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="E32" s="23" t="s">
         <v>130</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="33" ht="29.55" spans="1:5">
       <c r="A33" s="19"/>
       <c r="B33" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="20" t="s">
+      <c r="E33" s="23" t="s">
         <v>134</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="34" ht="29.55" spans="1:5">
       <c r="A34" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B34" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="E34" s="23" t="s">
         <v>138</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="35" ht="29.55" spans="1:5">
       <c r="A35" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B35" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="D35" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="E35" s="23" t="s">
         <v>142</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="36" ht="29.55" spans="1:5">
       <c r="A36" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B36" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="E36" s="23" t="s">
         <v>146</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="37" ht="29.55" spans="1:5">
       <c r="A37" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C37" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="E37" s="23" t="s">
         <v>149</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="38" ht="29.55" spans="1:5">
       <c r="A38" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B38" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="D38" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="C38" s="20" t="s">
+      <c r="E38" s="23" t="s">
         <v>153</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="39" ht="29.55" spans="1:5">
       <c r="A39" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="B39" s="20" t="s">
+      <c r="D39" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="E39" s="23" t="s">
         <v>158</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="40" ht="29.55" spans="1:5">
       <c r="A40" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" ht="43.95" spans="1:5">
       <c r="A41" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C41" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="D41" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="E41" s="23" t="s">
         <v>165</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="42" ht="43.95" spans="1:5">
       <c r="A42" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="C42" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="B42" s="20" t="s">
+      <c r="D42" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="E42" s="23" t="s">
         <v>170</v>
-      </c>
-      <c r="D42" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="43" ht="29.55" spans="1:5">
       <c r="A43" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B43" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="D43" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="C43" s="20" t="s">
+      <c r="E43" s="23" t="s">
         <v>174</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="E43" s="23" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="44" ht="29.55" spans="1:5">
       <c r="A44" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B44" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="D44" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="C44" s="20" t="s">
+      <c r="E44" s="23" t="s">
         <v>178</v>
-      </c>
-      <c r="D44" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="45" ht="29.55" spans="1:5">
       <c r="A45" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="C45" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="B45" s="20" t="s">
+      <c r="D45" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="C45" s="20" t="s">
+      <c r="E45" s="23" t="s">
         <v>183</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="46" ht="29.55" spans="1:5">
       <c r="A46" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C46" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E46" s="23" t="s">
         <v>186</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="E46" s="23" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="47" ht="29.55" spans="1:5">
       <c r="A47" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B47" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="D47" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="C47" s="20" t="s">
+      <c r="E47" s="23" t="s">
         <v>190</v>
-      </c>
-      <c r="D47" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="E47" s="23" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="48" ht="29.55" spans="1:5">
       <c r="A48" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B48" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="D48" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="C48" s="20" t="s">
+      <c r="E48" s="23" t="s">
         <v>194</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="E48" s="23" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="49" ht="29.55" spans="1:5">
       <c r="A49" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B49" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="D49" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="E49" s="23" t="s">
         <v>198</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="E49" s="23" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="50" ht="29.55" spans="1:5">
       <c r="A50" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B50" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="D50" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="C50" s="20" t="s">
+      <c r="E50" s="23" t="s">
         <v>202</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="51" ht="29.55" spans="1:5">
       <c r="A51" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="C51" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="B51" s="20" t="s">
+      <c r="D51" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="20" t="s">
+      <c r="E51" s="23" t="s">
         <v>207</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="52" ht="29.55" spans="1:5">
       <c r="A52" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B52" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="D52" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="E52" s="23" t="s">
         <v>211</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="E52" s="23" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="53" ht="29.55" spans="1:5">
       <c r="A53" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C53" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="E53" s="23" t="s">
         <v>214</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="E53" s="23" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="54" ht="29.55" spans="1:5">
       <c r="A54" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C54" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="E54" s="23" t="s">
         <v>217</v>
-      </c>
-      <c r="D54" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="E54" s="23" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="55" ht="29.55" spans="1:5">
       <c r="A55" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C55" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="E55" s="23" t="s">
         <v>220</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="E55" s="23" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="56" ht="29.55" spans="1:5">
       <c r="A56" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C56" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="E56" s="23" t="s">
         <v>223</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="E56" s="23" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="57" ht="29.55" spans="1:5">
       <c r="A57" s="23"/>
       <c r="B57" s="20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C57" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="E57" s="23" t="s">
         <v>226</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="E57" s="23" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="58" ht="29.55" spans="1:5">
       <c r="A58" s="23"/>
       <c r="B58" s="20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D58" s="23"/>
       <c r="E58" s="23" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -9892,53 +9872,53 @@
   <sheetData>
     <row r="1" ht="43.95" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="2" ht="43.95" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B2" s="4">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="3" ht="30.3" customHeight="1" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B3" s="4">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="4" ht="15.15" spans="1:5">
@@ -9954,41 +9934,41 @@
       <c r="C5" s="3"/>
       <c r="D5" s="1"/>
       <c r="E5" s="11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" ht="29.55" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B6" s="4">
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" ht="44.7" customHeight="1" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B7" s="4">
         <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" ht="15.15" spans="1:5">
@@ -10004,92 +9984,92 @@
       <c r="C9" s="3"/>
       <c r="D9" s="1"/>
       <c r="E9" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" ht="43.95" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B10" s="4">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" ht="43.95" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B11" s="4">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" ht="58.35" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B12" s="4">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" ht="43.95" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B13" s="4">
         <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" ht="43.95" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B14" s="4">
         <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="15" ht="15.15" spans="1:5">
@@ -10101,155 +10081,155 @@
     </row>
     <row r="16" ht="58.35" spans="1:5">
       <c r="A16" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="17" ht="58.35" spans="1:5">
       <c r="A17" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="D17" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="18" ht="58.35" spans="1:5">
       <c r="A18" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="D18" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="19" ht="58.35" spans="1:5">
       <c r="A19" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="D19" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="20" ht="58.35" spans="1:5">
       <c r="A20" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="D20" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="21" ht="58.35" spans="1:5">
       <c r="A21" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="D21" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="22" ht="58.35" spans="1:5">
       <c r="A22" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="D22" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="23" ht="58.35" spans="1:5">
       <c r="A23" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="D23" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>295</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="24" ht="58.35" spans="1:5">
       <c r="A24" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="D24" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>299</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="25" ht="15.15" spans="1:5">
@@ -10261,31 +10241,31 @@
     </row>
     <row r="26" ht="58.35" spans="1:5">
       <c r="A26" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="E26" s="14"/>
     </row>
     <row r="27" ht="44.7" customHeight="1" spans="1:5">
       <c r="A27" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="D27" s="15" t="s">
         <v>307</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>309</v>
       </c>
       <c r="E27" s="14"/>
     </row>
@@ -10301,7 +10281,7 @@
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="16" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E29" s="14"/>
     </row>
@@ -10317,7 +10297,7 @@
       <c r="B31" s="2"/>
       <c r="C31" s="4"/>
       <c r="D31" s="16" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E31" s="14"/>
     </row>
@@ -10333,7 +10313,7 @@
       <c r="B33" s="2"/>
       <c r="C33" s="4"/>
       <c r="D33" s="16" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E33" s="14"/>
     </row>
@@ -10349,7 +10329,7 @@
       <c r="B35" s="2"/>
       <c r="C35" s="4"/>
       <c r="D35" s="16" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E35" s="14"/>
     </row>
@@ -10365,112 +10345,112 @@
       <c r="B37" s="2"/>
       <c r="C37" s="4"/>
       <c r="D37" s="12" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E37" s="14"/>
     </row>
     <row r="38" ht="58.35" spans="1:5">
       <c r="A38" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="D38" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>318</v>
       </c>
       <c r="E38" s="14"/>
     </row>
     <row r="39" ht="58.35" spans="1:5">
       <c r="A39" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>321</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E39" s="14"/>
     </row>
     <row r="40" ht="58.35" spans="1:5">
       <c r="A40" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>324</v>
-      </c>
       <c r="D40" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E40" s="14"/>
     </row>
     <row r="41" ht="58.35" spans="1:5">
       <c r="A41" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>327</v>
-      </c>
       <c r="D41" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E41" s="14"/>
     </row>
     <row r="42" ht="58.35" spans="1:5">
       <c r="A42" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>330</v>
-      </c>
       <c r="D42" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E42" s="14"/>
     </row>
     <row r="43" ht="58.35" spans="1:5">
       <c r="A43" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>333</v>
-      </c>
       <c r="D43" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E43" s="14"/>
     </row>
     <row r="44" ht="58.35" spans="1:5">
       <c r="A44" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>336</v>
-      </c>
       <c r="D44" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E44" s="14"/>
     </row>
@@ -10502,856 +10482,856 @@
   <sheetData>
     <row r="1" ht="70.95" spans="1:4">
       <c r="A1" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>338</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="2" ht="29.55" spans="1:4">
       <c r="A2" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>342</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="3" ht="29.55" spans="1:4">
       <c r="A3" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>346</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="4" ht="29.55" spans="1:4">
       <c r="A4" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>350</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="5" ht="29.55" spans="1:4">
       <c r="A5" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>354</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="6" ht="29.55" spans="1:4">
       <c r="A6" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>358</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="7" ht="29.55" spans="1:4">
       <c r="A7" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>362</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="8" ht="29.55" spans="1:4">
       <c r="A8" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>366</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="9" ht="29.55" spans="1:4">
       <c r="A9" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>370</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="10" ht="29.55" spans="1:4">
       <c r="A10" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>374</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="11" ht="29.55" spans="1:4">
       <c r="A11" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>378</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="12" ht="29.55" spans="1:4">
       <c r="A12" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>382</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="13" ht="29.55" spans="1:4">
       <c r="A13" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>386</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="14" ht="29.55" spans="1:4">
       <c r="A14" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>390</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="15" ht="29.55" spans="1:4">
       <c r="A15" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="D15" s="8" t="s">
         <v>394</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="16" ht="29.55" spans="1:4">
       <c r="A16" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>398</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="17" ht="29.55" spans="1:4">
       <c r="A17" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>402</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="18" ht="29.55" spans="1:4">
       <c r="A18" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>406</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="19" ht="29.55" spans="1:4">
       <c r="A19" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>410</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="20" ht="29.55" spans="1:4">
       <c r="A20" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="D20" s="8" t="s">
         <v>414</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="21" ht="29.55" spans="1:4">
       <c r="A21" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="D21" s="8" t="s">
         <v>418</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="22" ht="29.55" spans="1:4">
       <c r="A22" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="D22" s="8" t="s">
         <v>422</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="23" ht="29.55" spans="1:4">
       <c r="A23" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="D23" s="8" t="s">
         <v>426</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="24" ht="29.55" spans="1:4">
       <c r="A24" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="D24" s="8" t="s">
         <v>430</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="25" ht="29.55" spans="1:4">
       <c r="A25" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="D25" s="8" t="s">
         <v>434</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="26" ht="29.55" spans="1:4">
       <c r="A26" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>437</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="27" ht="29.55" spans="1:4">
       <c r="A27" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>440</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="28" ht="29.55" spans="1:4">
       <c r="A28" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>443</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="29" ht="29.55" spans="1:4">
       <c r="A29" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>446</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="30" ht="29.55" spans="1:4">
       <c r="A30" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>449</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="31" ht="29.55" spans="1:4">
       <c r="A31" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>452</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="32" ht="29.55" spans="1:4">
       <c r="A32" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>455</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="33" ht="29.55" spans="1:4">
       <c r="A33" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>458</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="34" ht="29.55" spans="1:4">
       <c r="A34" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>461</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="35" ht="29.55" spans="1:4">
       <c r="A35" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>464</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="36" ht="57.75" spans="1:4">
       <c r="A36" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B36" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>467</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="37" ht="29.55" spans="1:4">
       <c r="A37" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B37" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="D37" s="8" t="s">
         <v>470</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="38" ht="29.55" spans="1:4">
       <c r="A38" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B38" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>473</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="39" ht="29.55" spans="1:4">
       <c r="A39" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B39" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>476</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="40" ht="29.55" spans="1:4">
       <c r="A40" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B40" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="D40" s="8" t="s">
         <v>479</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="41" ht="29.55" spans="1:4">
       <c r="A41" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>482</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="42" ht="29.55" spans="1:4">
       <c r="A42" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="43" ht="29.55" spans="1:4">
       <c r="A43" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B43" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="D43" s="8" t="s">
         <v>487</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="44" ht="29.55" spans="1:4">
       <c r="A44" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="45" ht="43.95" spans="1:4">
       <c r="A45" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B45" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="D45" s="8" t="s">
         <v>491</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="46" ht="43.95" spans="1:4">
       <c r="A46" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B46" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="D46" s="8" t="s">
         <v>494</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="47" ht="29.55" spans="1:4">
       <c r="A47" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B47" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="D47" s="8" t="s">
         <v>497</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="48" ht="29.55" spans="1:4">
       <c r="A48" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B48" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="D48" s="8" t="s">
         <v>500</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="49" ht="57.75" spans="1:4">
       <c r="A49" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="50" ht="29.55" spans="1:4">
       <c r="A50" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="51" ht="29.55" spans="1:4">
       <c r="A51" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B51" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="D51" s="8" t="s">
         <v>507</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="52" ht="29.55" spans="1:4">
       <c r="A52" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="53" ht="29.55" spans="1:4">
       <c r="A53" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="54" ht="29.55" spans="1:4">
       <c r="A54" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="55" ht="29.55" spans="1:4">
       <c r="A55" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B55" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="D55" s="8" t="s">
         <v>516</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="56" ht="29.55" spans="1:4">
       <c r="A56" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B56" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="D56" s="8" t="s">
         <v>519</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="57" ht="29.55" spans="1:4">
       <c r="A57" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="58" ht="29.55" spans="1:4">
       <c r="A58" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="59" ht="29.55" spans="1:4">
       <c r="A59" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="60" ht="29.55" spans="1:4">
       <c r="A60" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="61" ht="29.55" spans="1:4">
       <c r="A61" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
   </sheetData>
@@ -11375,7 +11355,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -11383,380 +11363,380 @@
     </row>
     <row r="2" ht="29.55" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" ht="29.55" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" ht="29.55" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" ht="29.55" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" ht="29.55" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" ht="29.55" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" ht="29.55" spans="1:4">
       <c r="A8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="9" ht="29.55" spans="1:4">
       <c r="A9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10" ht="29.55" spans="1:4">
       <c r="A10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="11" ht="29.55" spans="1:4">
       <c r="A11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12" ht="29.55" spans="1:4">
       <c r="A12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13" ht="29.55" spans="1:4">
       <c r="A13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="D13" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="14" ht="29.55" spans="1:4">
       <c r="A14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="15" ht="29.55" spans="1:4">
       <c r="A15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="16" ht="29.55" spans="1:4">
       <c r="A16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="17" ht="29.55" spans="1:4">
       <c r="A17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="D17" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="18" ht="29.55" spans="1:4">
       <c r="A18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="19" ht="29.55" spans="1:4">
       <c r="A19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="20" ht="29.55" spans="1:4">
       <c r="A20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="21" ht="29.55" spans="1:4">
       <c r="A21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="22" ht="29.55" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="23" ht="29.55" spans="1:4">
       <c r="A23" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="24" ht="29.55" spans="1:4">
       <c r="A24" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" ht="43.95" spans="1:4">
       <c r="A25" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="26" ht="43.95" spans="1:4">
       <c r="A26" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="27" ht="29.55" spans="1:4">
       <c r="A27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="D27" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="28" ht="29.55" spans="1:4">
       <c r="A28" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="D28" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>208</v>
       </c>
     </row>
   </sheetData>
